--- a/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260540917579901</v>
+        <v>1.27314655810243</v>
       </c>
       <c r="C3" t="n">
-        <v>4.599367130488846</v>
+        <v>4.629222078174991</v>
       </c>
       <c r="D3" t="n">
-        <v>6.156456498711527</v>
+        <v>6.051782558484732</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01636454678027</v>
+        <v>11.95415119476215</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391798958638011</v>
+        <v>1.42061411385958</v>
       </c>
       <c r="C4" t="n">
-        <v>5.031941230689997</v>
+        <v>5.132596818210525</v>
       </c>
       <c r="D4" t="n">
-        <v>6.429156150191482</v>
+        <v>6.315196132868274</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85289633951949</v>
+        <v>12.86840706493838</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.564273057964423</v>
+        <v>1.611249152175675</v>
       </c>
       <c r="C5" t="n">
-        <v>5.600194694151916</v>
+        <v>5.752446835912294</v>
       </c>
       <c r="D5" t="n">
-        <v>6.706849321793098</v>
+        <v>6.623049292293345</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87131707390944</v>
+        <v>13.98674528038131</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.760936318130909</v>
+        <v>1.821821329210914</v>
       </c>
       <c r="C6" t="n">
-        <v>6.28277054754221</v>
+        <v>6.5056081072805</v>
       </c>
       <c r="D6" t="n">
-        <v>7.154400493189311</v>
+        <v>6.927691473620312</v>
       </c>
       <c r="E6" t="n">
-        <v>15.19810735886243</v>
+        <v>15.25512091011173</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.983390399012034</v>
+        <v>2.055081761821445</v>
       </c>
       <c r="C7" t="n">
-        <v>7.071757195283729</v>
+        <v>7.388647518415131</v>
       </c>
       <c r="D7" t="n">
-        <v>7.587758255750664</v>
+        <v>7.313782100647046</v>
       </c>
       <c r="E7" t="n">
-        <v>16.64290585004643</v>
+        <v>16.75751138088362</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.208777351350481</v>
+        <v>1.252466277734338</v>
       </c>
       <c r="C8" t="n">
-        <v>4.712760506994734</v>
+        <v>5.015682212515498</v>
       </c>
       <c r="D8" t="n">
-        <v>5.819935748956872</v>
+        <v>5.615315848857885</v>
       </c>
       <c r="E8" t="n">
-        <v>11.74147360730209</v>
+        <v>11.88346433910772</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.51756536719735</v>
+        <v>1.5685842484514</v>
       </c>
       <c r="C9" t="n">
-        <v>5.664631405102815</v>
+        <v>6.09187998930305</v>
       </c>
       <c r="D9" t="n">
-        <v>6.325530015843888</v>
+        <v>6.175579324482421</v>
       </c>
       <c r="E9" t="n">
-        <v>13.50772678814405</v>
+        <v>13.83604356223687</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.843611465297366</v>
+        <v>1.904919062683414</v>
       </c>
       <c r="C10" t="n">
-        <v>6.772879449015073</v>
+        <v>7.28907060327799</v>
       </c>
       <c r="D10" t="n">
-        <v>6.878308216986285</v>
+        <v>6.690899850978445</v>
       </c>
       <c r="E10" t="n">
-        <v>15.49479913129872</v>
+        <v>15.88488951693985</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.17521346997018</v>
+        <v>2.252617444295891</v>
       </c>
       <c r="C11" t="n">
-        <v>8.012476966895628</v>
+        <v>8.588529458875259</v>
       </c>
       <c r="D11" t="n">
-        <v>7.412057503834005</v>
+        <v>7.237415308844531</v>
       </c>
       <c r="E11" t="n">
-        <v>17.59974794069981</v>
+        <v>18.07856221201568</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.537377079496055</v>
+        <v>2.602508694061196</v>
       </c>
       <c r="C12" t="n">
-        <v>9.368364571898274</v>
+        <v>9.987263769827077</v>
       </c>
       <c r="D12" t="n">
-        <v>7.934316907349941</v>
+        <v>7.762332525613223</v>
       </c>
       <c r="E12" t="n">
-        <v>19.84005855874427</v>
+        <v>20.35210498950149</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.883390819286394</v>
+        <v>2.937485778974783</v>
       </c>
       <c r="C13" t="n">
-        <v>10.78939286337261</v>
+        <v>11.47695186139045</v>
       </c>
       <c r="D13" t="n">
-        <v>8.468799352324757</v>
+        <v>8.374770920709794</v>
       </c>
       <c r="E13" t="n">
-        <v>22.14158303498376</v>
+        <v>22.78920856107503</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.673997645465321</v>
+        <v>1.694712522024929</v>
       </c>
       <c r="C14" t="n">
-        <v>7.68929345658708</v>
+        <v>8.167424223509363</v>
       </c>
       <c r="D14" t="n">
-        <v>6.416634272617855</v>
+        <v>6.39123645950899</v>
       </c>
       <c r="E14" t="n">
-        <v>15.77992537467026</v>
+        <v>16.25337320504328</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.72431221530797</v>
+        <v>1.729574383002733</v>
       </c>
       <c r="C15" t="n">
-        <v>8.288591525167503</v>
+        <v>8.791727406116951</v>
       </c>
       <c r="D15" t="n">
-        <v>6.454137034920084</v>
+        <v>6.467194279386566</v>
       </c>
       <c r="E15" t="n">
-        <v>16.46704077539556</v>
+        <v>16.98849606850625</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.028889623073501</v>
+        <v>1.996531218741526</v>
       </c>
       <c r="C16" t="n">
-        <v>9.861223720169342</v>
+        <v>10.42761360570341</v>
       </c>
       <c r="D16" t="n">
-        <v>6.959511300635215</v>
+        <v>6.972283838267464</v>
       </c>
       <c r="E16" t="n">
-        <v>18.84962464387806</v>
+        <v>19.3964286627124</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.645900026169778</v>
+        <v>1.588899754461208</v>
       </c>
       <c r="C17" t="n">
-        <v>9.206427453867846</v>
+        <v>9.665698847391548</v>
       </c>
       <c r="D17" t="n">
-        <v>6.488576744385061</v>
+        <v>6.517548119137385</v>
       </c>
       <c r="E17" t="n">
-        <v>17.34090422442269</v>
+        <v>17.77214672099014</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.898169916253038</v>
+        <v>1.804206843479576</v>
       </c>
       <c r="C18" t="n">
-        <v>10.82039122721847</v>
+        <v>11.36041136941648</v>
       </c>
       <c r="D18" t="n">
-        <v>6.914763240275645</v>
+        <v>7.026937732962885</v>
       </c>
       <c r="E18" t="n">
-        <v>19.63332438374716</v>
+        <v>20.19155594585894</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.918973150106028</v>
+        <v>1.804903884349591</v>
       </c>
       <c r="C19" t="n">
-        <v>11.67048656432579</v>
+        <v>12.23249785509892</v>
       </c>
       <c r="D19" t="n">
-        <v>7.021832644900802</v>
+        <v>7.179982382577921</v>
       </c>
       <c r="E19" t="n">
-        <v>20.61129235933262</v>
+        <v>21.21738412202643</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.149497328540221</v>
+        <v>2.000477844512598</v>
       </c>
       <c r="C20" t="n">
-        <v>13.53992072527552</v>
+        <v>14.0933908110217</v>
       </c>
       <c r="D20" t="n">
-        <v>7.488300249096632</v>
+        <v>7.67516610712297</v>
       </c>
       <c r="E20" t="n">
-        <v>23.17771830291237</v>
+        <v>23.76903476265727</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.284950665226396</v>
+        <v>1.188533223192316</v>
       </c>
       <c r="C21" t="n">
-        <v>10.08784054274063</v>
+        <v>10.42721108914467</v>
       </c>
       <c r="D21" t="n">
-        <v>6.234372811324436</v>
+        <v>6.436750283077872</v>
       </c>
       <c r="E21" t="n">
-        <v>17.60716401929147</v>
+        <v>18.05249459541486</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27314655810243</v>
+        <v>1.270191497512647</v>
       </c>
       <c r="C3" t="n">
-        <v>4.629222078174991</v>
+        <v>4.670759823541673</v>
       </c>
       <c r="D3" t="n">
-        <v>6.051782558484732</v>
+        <v>6.09473402054553</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95415119476215</v>
+        <v>12.03568534159985</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.42061411385958</v>
+        <v>1.433323576315029</v>
       </c>
       <c r="C4" t="n">
-        <v>5.132596818210525</v>
+        <v>5.264254494963334</v>
       </c>
       <c r="D4" t="n">
-        <v>6.315196132868274</v>
+        <v>6.316804553480698</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86840706493838</v>
+        <v>13.01438262475906</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.611249152175675</v>
+        <v>1.649267785232588</v>
       </c>
       <c r="C5" t="n">
-        <v>5.752446835912294</v>
+        <v>6.038706326532434</v>
       </c>
       <c r="D5" t="n">
-        <v>6.623049292293345</v>
+        <v>6.672696885819046</v>
       </c>
       <c r="E5" t="n">
-        <v>13.98674528038131</v>
+        <v>14.36067099758407</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.821821329210914</v>
+        <v>1.887753025591357</v>
       </c>
       <c r="C6" t="n">
-        <v>6.5056081072805</v>
+        <v>7.002708786743197</v>
       </c>
       <c r="D6" t="n">
-        <v>6.927691473620312</v>
+        <v>7.022779894555494</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25512091011173</v>
+        <v>15.91324170689005</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.055081761821445</v>
+        <v>2.150668774488979</v>
       </c>
       <c r="C7" t="n">
-        <v>7.388647518415131</v>
+        <v>8.101735570226138</v>
       </c>
       <c r="D7" t="n">
-        <v>7.313782100647046</v>
+        <v>7.389534212950622</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75751138088362</v>
+        <v>17.64193855766574</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.252466277734338</v>
+        <v>1.349629687295771</v>
       </c>
       <c r="C8" t="n">
-        <v>5.015682212515498</v>
+        <v>5.694172680019802</v>
       </c>
       <c r="D8" t="n">
-        <v>5.615315848857885</v>
+        <v>5.707261124139016</v>
       </c>
       <c r="E8" t="n">
-        <v>11.88346433910772</v>
+        <v>12.75106349145459</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.5685842484514</v>
+        <v>1.686390325810254</v>
       </c>
       <c r="C9" t="n">
-        <v>6.09187998930305</v>
+        <v>7.01651717875893</v>
       </c>
       <c r="D9" t="n">
-        <v>6.175579324482421</v>
+        <v>6.192324371020287</v>
       </c>
       <c r="E9" t="n">
-        <v>13.83604356223687</v>
+        <v>14.89523187558947</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.904919062683414</v>
+        <v>2.04466989908558</v>
       </c>
       <c r="C10" t="n">
-        <v>7.28907060327799</v>
+        <v>8.46359408433422</v>
       </c>
       <c r="D10" t="n">
-        <v>6.690899850978445</v>
+        <v>6.716622697100999</v>
       </c>
       <c r="E10" t="n">
-        <v>15.88488951693985</v>
+        <v>17.2248866805208</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.252617444295891</v>
+        <v>2.400902597148693</v>
       </c>
       <c r="C11" t="n">
-        <v>8.588529458875259</v>
+        <v>10.06881089359335</v>
       </c>
       <c r="D11" t="n">
-        <v>7.237415308844531</v>
+        <v>7.245071571874433</v>
       </c>
       <c r="E11" t="n">
-        <v>18.07856221201568</v>
+        <v>19.71478506261647</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.602508694061196</v>
+        <v>2.746939378811964</v>
       </c>
       <c r="C12" t="n">
-        <v>9.987263769827077</v>
+        <v>11.75027515801629</v>
       </c>
       <c r="D12" t="n">
-        <v>7.762332525613223</v>
+        <v>7.752302671889159</v>
       </c>
       <c r="E12" t="n">
-        <v>20.35210498950149</v>
+        <v>22.24951720871741</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.937485778974783</v>
+        <v>3.079578853438555</v>
       </c>
       <c r="C13" t="n">
-        <v>11.47695186139045</v>
+        <v>13.4610952548563</v>
       </c>
       <c r="D13" t="n">
-        <v>8.374770920709794</v>
+        <v>8.338814377516529</v>
       </c>
       <c r="E13" t="n">
-        <v>22.78920856107503</v>
+        <v>24.87948848581139</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.694712522024929</v>
+        <v>1.762757455406275</v>
       </c>
       <c r="C14" t="n">
-        <v>8.167424223509363</v>
+        <v>9.470586308649535</v>
       </c>
       <c r="D14" t="n">
-        <v>6.39123645950899</v>
+        <v>6.34672401859844</v>
       </c>
       <c r="E14" t="n">
-        <v>16.25337320504328</v>
+        <v>17.58006778265425</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.729574383002733</v>
+        <v>1.802380792749677</v>
       </c>
       <c r="C15" t="n">
-        <v>8.791727406116951</v>
+        <v>10.24759052917567</v>
       </c>
       <c r="D15" t="n">
-        <v>6.467194279386566</v>
+        <v>6.376785133302477</v>
       </c>
       <c r="E15" t="n">
-        <v>16.98849606850625</v>
+        <v>18.42675645522783</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.996531218741526</v>
+        <v>2.084446725656828</v>
       </c>
       <c r="C16" t="n">
-        <v>10.42761360570341</v>
+        <v>12.09023279527651</v>
       </c>
       <c r="D16" t="n">
-        <v>6.972283838267464</v>
+        <v>6.952884503631548</v>
       </c>
       <c r="E16" t="n">
-        <v>19.3964286627124</v>
+        <v>21.12756402456489</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.588899754461208</v>
+        <v>1.664494327688212</v>
       </c>
       <c r="C17" t="n">
-        <v>9.665698847391548</v>
+        <v>11.08161465636447</v>
       </c>
       <c r="D17" t="n">
-        <v>6.517548119137385</v>
+        <v>6.483599283524531</v>
       </c>
       <c r="E17" t="n">
-        <v>17.77214672099014</v>
+        <v>19.22970826757721</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.804206843479576</v>
+        <v>1.88906911503467</v>
       </c>
       <c r="C18" t="n">
-        <v>11.36041136941648</v>
+        <v>12.92344207187078</v>
       </c>
       <c r="D18" t="n">
-        <v>7.026937732962885</v>
+        <v>7.003837209481959</v>
       </c>
       <c r="E18" t="n">
-        <v>20.19155594585894</v>
+        <v>21.81634839638741</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.804903884349591</v>
+        <v>1.884297821192031</v>
       </c>
       <c r="C19" t="n">
-        <v>12.23249785509892</v>
+        <v>13.77670845406281</v>
       </c>
       <c r="D19" t="n">
-        <v>7.179982382577921</v>
+        <v>7.15046122911122</v>
       </c>
       <c r="E19" t="n">
-        <v>21.21738412202643</v>
+        <v>22.81146750436606</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.000477844512598</v>
+        <v>2.076435664390174</v>
       </c>
       <c r="C20" t="n">
-        <v>14.0933908110217</v>
+        <v>15.73739606412229</v>
       </c>
       <c r="D20" t="n">
-        <v>7.67516610712297</v>
+        <v>7.583814483242805</v>
       </c>
       <c r="E20" t="n">
-        <v>23.76903476265727</v>
+        <v>25.39764621175527</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.188533223192316</v>
+        <v>1.225996715586374</v>
       </c>
       <c r="C21" t="n">
-        <v>10.42721108914467</v>
+        <v>11.4974338964982</v>
       </c>
       <c r="D21" t="n">
-        <v>6.436750283077872</v>
+        <v>6.366781124196202</v>
       </c>
       <c r="E21" t="n">
-        <v>18.05249459541486</v>
+        <v>19.09021173628078</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_21_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270191497512647</v>
+        <v>2.605145594918781</v>
       </c>
       <c r="C3" t="n">
-        <v>4.670759823541673</v>
+        <v>7.815631738003107</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09473402054553</v>
+        <v>8.151498080803901</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03568534159985</v>
+        <v>18.57227541372579</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.433323576315029</v>
+        <v>1.097065633690886</v>
       </c>
       <c r="C4" t="n">
-        <v>5.264254494963334</v>
+        <v>4.824875972259967</v>
       </c>
       <c r="D4" t="n">
-        <v>6.316804553480698</v>
+        <v>5.759550002607213</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01438262475906</v>
+        <v>11.68149160855807</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.649267785232588</v>
+        <v>1.205085566000221</v>
       </c>
       <c r="C5" t="n">
-        <v>6.038706326532434</v>
+        <v>5.87098566516003</v>
       </c>
       <c r="D5" t="n">
-        <v>6.672696885819046</v>
+        <v>6.034778314564895</v>
       </c>
       <c r="E5" t="n">
-        <v>14.36067099758407</v>
+        <v>13.11084954572515</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.887753025591357</v>
+        <v>1.319673723686572</v>
       </c>
       <c r="C6" t="n">
-        <v>7.002708786743197</v>
+        <v>7.262927704100448</v>
       </c>
       <c r="D6" t="n">
-        <v>7.022779894555494</v>
+        <v>6.41777450989445</v>
       </c>
       <c r="E6" t="n">
-        <v>15.91324170689005</v>
+        <v>15.00037593768147</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.150668774488979</v>
+        <v>1.425360355102091</v>
       </c>
       <c r="C7" t="n">
-        <v>8.101735570226138</v>
+        <v>8.855823964522937</v>
       </c>
       <c r="D7" t="n">
-        <v>7.389534212950622</v>
+        <v>6.851752633824931</v>
       </c>
       <c r="E7" t="n">
-        <v>17.64193855766574</v>
+        <v>17.13293695344996</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.349629687295771</v>
+        <v>1.537815057427691</v>
       </c>
       <c r="C8" t="n">
-        <v>5.694172680019802</v>
+        <v>10.5653463138534</v>
       </c>
       <c r="D8" t="n">
-        <v>5.707261124139016</v>
+        <v>7.262573271571555</v>
       </c>
       <c r="E8" t="n">
-        <v>12.75106349145459</v>
+        <v>19.36573464285264</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.686390325810254</v>
+        <v>1.625171679865079</v>
       </c>
       <c r="C9" t="n">
-        <v>7.01651717875893</v>
+        <v>12.45121512997901</v>
       </c>
       <c r="D9" t="n">
-        <v>6.192324371020287</v>
+        <v>7.728022307839204</v>
       </c>
       <c r="E9" t="n">
-        <v>14.89523187558947</v>
+        <v>21.80440911768329</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.04466989908558</v>
+        <v>1.019643165630737</v>
       </c>
       <c r="C10" t="n">
-        <v>8.46359408433422</v>
+        <v>8.771532855840595</v>
       </c>
       <c r="D10" t="n">
-        <v>6.716622697100999</v>
+        <v>6.082319726890689</v>
       </c>
       <c r="E10" t="n">
-        <v>17.2248866805208</v>
+        <v>15.87349574836202</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.400902597148693</v>
+        <v>0.9322283500446013</v>
       </c>
       <c r="C11" t="n">
-        <v>10.06881089359335</v>
+        <v>9.720087670206819</v>
       </c>
       <c r="D11" t="n">
-        <v>7.245071571874433</v>
+        <v>5.955183399190727</v>
       </c>
       <c r="E11" t="n">
-        <v>19.71478506261647</v>
+        <v>16.60749941944215</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.746939378811964</v>
+        <v>0.9749049227482101</v>
       </c>
       <c r="C12" t="n">
-        <v>11.75027515801629</v>
+        <v>11.68966009698973</v>
       </c>
       <c r="D12" t="n">
-        <v>7.752302671889159</v>
+        <v>6.346164422407019</v>
       </c>
       <c r="E12" t="n">
-        <v>22.24951720871741</v>
+        <v>19.01072944214496</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.079578853438555</v>
+        <v>0.7540804116319751</v>
       </c>
       <c r="C13" t="n">
-        <v>13.4610952548563</v>
+        <v>11.17641221468654</v>
       </c>
       <c r="D13" t="n">
-        <v>8.338814377516529</v>
+        <v>5.794019696061571</v>
       </c>
       <c r="E13" t="n">
-        <v>24.87948848581139</v>
+        <v>17.72451232238009</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.762757455406275</v>
+        <v>0.7913770069163113</v>
       </c>
       <c r="C14" t="n">
-        <v>9.470586308649535</v>
+        <v>13.12998215389023</v>
       </c>
       <c r="D14" t="n">
-        <v>6.34672401859844</v>
+        <v>6.114609408883366</v>
       </c>
       <c r="E14" t="n">
-        <v>17.58006778265425</v>
+        <v>20.0359685696899</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.802380792749677</v>
+        <v>0.7430946548214532</v>
       </c>
       <c r="C15" t="n">
-        <v>10.24759052917567</v>
+        <v>14.15822542941016</v>
       </c>
       <c r="D15" t="n">
-        <v>6.376785133302477</v>
+        <v>6.15280921205561</v>
       </c>
       <c r="E15" t="n">
-        <v>18.42675645522783</v>
+        <v>21.05412929628723</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.084446725656828</v>
+        <v>0.7911512049443347</v>
       </c>
       <c r="C16" t="n">
-        <v>12.09023279527651</v>
+        <v>16.30166537461518</v>
       </c>
       <c r="D16" t="n">
-        <v>6.952884503631548</v>
+        <v>6.514082549741394</v>
       </c>
       <c r="E16" t="n">
-        <v>21.12756402456489</v>
+        <v>23.60689912930091</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.664494327688212</v>
+        <v>0.467086105249505</v>
       </c>
       <c r="C17" t="n">
-        <v>11.08161465636447</v>
+        <v>11.92395418660823</v>
       </c>
       <c r="D17" t="n">
-        <v>6.483599283524531</v>
+        <v>5.413828080114951</v>
       </c>
       <c r="E17" t="n">
-        <v>19.22970826757721</v>
+        <v>17.80486837197269</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.88906911503467</v>
+        <v>0.3584753567286804</v>
       </c>
       <c r="C18" t="n">
-        <v>12.92344207187078</v>
+        <v>10.65262036203974</v>
       </c>
       <c r="D18" t="n">
-        <v>7.003837209481959</v>
+        <v>4.927538989770379</v>
       </c>
       <c r="E18" t="n">
-        <v>21.81634839638741</v>
+        <v>15.9386347085388</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.884297821192031</v>
+        <v>0.4101349209261475</v>
       </c>
       <c r="C19" t="n">
-        <v>13.77670845406281</v>
+        <v>12.96306540921418</v>
       </c>
       <c r="D19" t="n">
-        <v>7.15046122911122</v>
+        <v>5.38760559893452</v>
       </c>
       <c r="E19" t="n">
-        <v>22.81146750436606</v>
+        <v>18.76080592907485</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.076435664390174</v>
+        <v>0.4584172730210057</v>
       </c>
       <c r="C20" t="n">
-        <v>15.73739606412229</v>
+        <v>15.35074454828172</v>
       </c>
       <c r="D20" t="n">
-        <v>7.583814483242805</v>
+        <v>5.821449726918226</v>
       </c>
       <c r="E20" t="n">
-        <v>25.39764621175527</v>
+        <v>21.63061154822095</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.225996715586374</v>
+        <v>0.498148602611874</v>
       </c>
       <c r="C21" t="n">
-        <v>11.4974338964982</v>
+        <v>17.79822194001493</v>
       </c>
       <c r="D21" t="n">
-        <v>6.366781124196202</v>
+        <v>6.272336995047659</v>
       </c>
       <c r="E21" t="n">
-        <v>19.09021173628078</v>
+        <v>24.56870753767447</v>
       </c>
     </row>
   </sheetData>
